--- a/361-preparation-publication-release-407/ig/all-profiles.xlsx
+++ b/361-preparation-publication-release-407/ig/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.0.6</t>
+    <t>4.0.7</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T16:13:39+00:00</t>
+    <t>2026-06-26T16:22:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
